--- a/CNA01D.xlsx
+++ b/CNA01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="133">
   <si>
     <t/>
   </si>
@@ -82,12 +82,6 @@
     <t>IDM CD WNT 2'S L/XL</t>
   </si>
   <si>
-    <t>20130887</t>
-  </si>
-  <si>
-    <t>IDM CD WNT BMB2S S/M</t>
-  </si>
-  <si>
     <t>20140419</t>
   </si>
   <si>
@@ -392,12 +386,6 @@
   </si>
   <si>
     <t>IDM CD MEN CH-25 L</t>
-  </si>
-  <si>
-    <t>20053891</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA M</t>
   </si>
   <si>
     <t>20053892</t>
@@ -814,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1018,10 +1006,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1026,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>15</v>
@@ -1055,10 +1043,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>15</v>
@@ -1098,7 +1086,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>15</v>
@@ -1118,7 +1106,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>15</v>
@@ -1158,7 +1146,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>15</v>
@@ -1198,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>15</v>
@@ -1238,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>15</v>
@@ -1246,10 +1234,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1258,7 +1246,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>15</v>
@@ -1266,22 +1254,22 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1295,13 +1283,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1318,7 +1306,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>15</v>
@@ -1338,7 +1326,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>15</v>
@@ -1358,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>15</v>
@@ -1378,7 +1366,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>15</v>
@@ -1398,7 +1386,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
@@ -1418,7 +1406,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>15</v>
@@ -1426,10 +1414,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1438,7 +1426,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1455,13 +1443,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,7 +1486,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1518,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1558,7 +1546,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1578,7 +1566,7 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1618,10 +1606,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1638,7 +1626,7 @@
         <v>18</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>15</v>
@@ -1658,7 +1646,7 @@
         <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>15</v>
@@ -1678,10 +1666,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1698,7 +1686,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1718,7 +1706,7 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1726,19 +1714,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1755,7 +1743,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
@@ -1775,10 +1763,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1795,10 +1783,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1815,7 +1803,7 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>11</v>
@@ -1835,10 +1823,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -1855,13 +1843,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>18</v>
@@ -1895,10 +1883,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>15</v>
@@ -1915,13 +1903,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1935,10 +1923,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -1955,10 +1943,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -1975,10 +1963,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -1995,10 +1983,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2015,10 +2003,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2035,52 +2023,12 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F63" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/CNA01D.xlsx
+++ b/CNA01D.xlsx
@@ -1609,7 +1609,7 @@
         <v>49</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,7 +1629,7 @@
         <v>49</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1649,7 +1649,7 @@
         <v>52</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">

--- a/CNA01D.xlsx
+++ b/CNA01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="121">
   <si>
     <t/>
   </si>
@@ -82,18 +82,18 @@
     <t>IDM CD WNT 2'S L/XL</t>
   </si>
   <si>
+    <t>20122827</t>
+  </si>
+  <si>
+    <t>GT MAN BOXER XL(NEW)</t>
+  </si>
+  <si>
     <t>20140419</t>
   </si>
   <si>
     <t>IDM CD WNT SOFT 2-XL</t>
   </si>
   <si>
-    <t>20122827</t>
-  </si>
-  <si>
-    <t>GT MAN BOXER XL(NEW)</t>
-  </si>
-  <si>
     <t>20122826</t>
   </si>
   <si>
@@ -220,85 +220,49 @@
     <t>LARIST KK ANKLE SOCK</t>
   </si>
   <si>
+    <t>20140363</t>
+  </si>
+  <si>
+    <t>LRST ANKLE MSTY 1+1</t>
+  </si>
+  <si>
+    <t>20092086</t>
+  </si>
+  <si>
+    <t>IDM SINGLET PTH M</t>
+  </si>
+  <si>
+    <t>20092087</t>
+  </si>
+  <si>
+    <t>IDM SINGLET PTH L</t>
+  </si>
+  <si>
+    <t>20092089</t>
+  </si>
+  <si>
+    <t>IDM SINGLET PTH XL</t>
+  </si>
+  <si>
+    <t>20077983</t>
+  </si>
+  <si>
+    <t>IDM KAOS R-NCK PT XL</t>
+  </si>
+  <si>
+    <t>20097477</t>
+  </si>
+  <si>
+    <t>IDM KAOS RN PUTIH L</t>
+  </si>
+  <si>
+    <t>20136272</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/M</t>
+  </si>
+  <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>20140363</t>
-  </si>
-  <si>
-    <t>LRST ANKLE MSTY 1+1</t>
-  </si>
-  <si>
-    <t>20092086</t>
-  </si>
-  <si>
-    <t>IDM SINGLET PTH M</t>
-  </si>
-  <si>
-    <t>20092087</t>
-  </si>
-  <si>
-    <t>IDM SINGLET PTH L</t>
-  </si>
-  <si>
-    <t>20092089</t>
-  </si>
-  <si>
-    <t>IDM SINGLET PTH XL</t>
-  </si>
-  <si>
-    <t>20077982</t>
-  </si>
-  <si>
-    <t>IDM KAOS R-NCK PTH M</t>
-  </si>
-  <si>
-    <t>20077983</t>
-  </si>
-  <si>
-    <t>IDM KAOS R-NCK PT XL</t>
-  </si>
-  <si>
-    <t>20097477</t>
-  </si>
-  <si>
-    <t>IDM KAOS RN PUTIH L</t>
-  </si>
-  <si>
-    <t>20077370</t>
-  </si>
-  <si>
-    <t>IDM KAOS V-NCK PTH M</t>
-  </si>
-  <si>
-    <t>20077371</t>
-  </si>
-  <si>
-    <t>IDM KAOS V-NCK PT XL</t>
-  </si>
-  <si>
-    <t>20081565</t>
-  </si>
-  <si>
-    <t>IDM KAOS V-NCK HTM M</t>
-  </si>
-  <si>
-    <t>20081566</t>
-  </si>
-  <si>
-    <t>IDM KAOS V-NCK HT XL</t>
-  </si>
-  <si>
-    <t>20097479</t>
-  </si>
-  <si>
-    <t>IDM KAOS V-NCK HTM L</t>
-  </si>
-  <si>
-    <t>20136272</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/M</t>
   </si>
   <si>
     <t>20136273</t>
@@ -802,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -989,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1006,10 +970,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1026,7 +990,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>15</v>
@@ -1306,7 +1270,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>15</v>
@@ -1326,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>15</v>
@@ -1346,7 +1310,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>15</v>
@@ -1366,7 +1330,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>15</v>
@@ -1386,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>15</v>
@@ -1406,7 +1370,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>15</v>
@@ -1414,10 +1378,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1426,7 +1390,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>15</v>
@@ -1434,10 +1398,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1454,10 +1418,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1474,10 +1438,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1494,10 +1458,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1514,10 +1478,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1526,7 +1490,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1534,10 +1498,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1546,7 +1510,7 @@
         <v>18</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1566,7 +1530,7 @@
         <v>18</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1586,7 +1550,7 @@
         <v>18</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1594,19 +1558,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1614,19 +1578,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1634,19 +1598,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1654,19 +1618,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1674,19 +1638,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1694,19 +1658,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1726,10 +1690,10 @@
         <v>49</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,10 +1710,10 @@
         <v>49</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,10 +1730,10 @@
         <v>49</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,10 +1747,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1803,10 +1767,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -1823,10 +1787,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -1843,13 +1807,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1863,13 +1827,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,13 +1847,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,129 +1870,9 @@
         <v>52</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F61" s="1" t="s">
         <v>5</v>
       </c>
     </row>
